--- a/PTBR/Lang/PTBR/Dialog/Drama/fiama.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/fiama.xlsx
@@ -491,7 +491,7 @@
           <t>You seem fine now.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Você parece bem agora.</t>
         </is>
@@ -516,9 +516,9 @@
           <t>...Is your head alright?</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...você está bem?  </t>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>...Sua cabeça está bem?</t>
         </is>
       </c>
     </row>
@@ -551,9 +551,9 @@
           <t>Thanks for saving me.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obrigado por me salvar.  </t>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Obrigada por me salvar.</t>
         </is>
       </c>
     </row>
@@ -586,9 +586,9 @@
           <t>Tell me the story of the ugly beast.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conte-me a história da fera feia.  </t>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>Conte-me a história da fera feia.</t>
         </is>
       </c>
     </row>
@@ -616,9 +616,9 @@
           <t>I have some questions.</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tenho algumas perguntas.  </t>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>Tenho algumas perguntas.</t>
         </is>
       </c>
     </row>
@@ -695,11 +695,10 @@
 I'm giving you one of my precious companions for a gift. What kind of animal do you like?</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Então você decidiu viver nesta terra. Desejo-lhe tudo de bom em seu novo lar.  _x000D_
-_x000D_
-Estou lhe dando um dos meus preciosos companheiros como presente. Que tipo de animal você gosta?  </t>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Então decidiu viver nesta terra. Desejo sorte no seu novo lar.
+Vou te dar uma das minhas companheiras preciosas de presente. Que tipo de bicho você gosta?</t>
         </is>
       </c>
     </row>
@@ -727,9 +726,9 @@
           <t>A dog!</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um cachorro!  </t>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Um cachorro!</t>
         </is>
       </c>
     </row>
@@ -757,9 +756,9 @@
           <t>A cat!</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um gato!  </t>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Um gato!</t>
         </is>
       </c>
     </row>
@@ -787,9 +786,9 @@
           <t>A bear!</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um urso!  </t>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Um urso!</t>
         </is>
       </c>
     </row>
@@ -817,9 +816,9 @@
           <t>A little girl!</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uma garotinha!  </t>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Uma garotinha!</t>
         </is>
       </c>
     </row>
@@ -942,11 +941,10 @@
 If you get separated from your companions, you can call them back from a tavern in a nearby town.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tudo bem. Cuide bem dele.  _x000D_
-_x000D_
-Se você se separar de seus companheiros, pode chamá-los de volta em uma taverna na cidade mais próxima.  </t>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>Beleza. Cuide bem dele.
+Se se separar dos seus companheiros, pode chamá-los de volta numa taverna de uma cidade próxima.</t>
         </is>
       </c>
     </row>
@@ -985,11 +983,10 @@
 ...Do you remember I asked you to take good care of it?</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O animal de estimação que lhe dei voltou para mim machucado.  _x000D_
-_x000D_
-...Você se lembra que pedi para que cuidasse bem dele?  </t>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>O bicho que te dei voltou para mim machucado.
+...Lembra que pedi para cuidar bem dele?</t>
         </is>
       </c>
     </row>
@@ -1035,10 +1032,10 @@
 I thought you were a goner when I found you in the old forest. I'm glad you are okay.</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não precisa me agradecer, você estava no meu caminho.  
-Pensei que você não fosse sobreviver quando o encontrei na floresta antiga. Fico feliz que esteja bem.  </t>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>Não precisa me agradecer, você estava no meu caminho.
+Achei que você era um caso perdido quando te encontrei na floresta antiga. Fico feliz que esteja bem.</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1069,10 @@
 A woman ran into the hut and fell down one day. She was wounded by a wolf. The prince hesitated but took care of the woman anyway. She, of course, was frightened by the sight of the man and wept.</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Era uma vez um príncipe que foi magicamente transformado em uma fera feia. Desesperado com sua aparência, ele abandonou seu país e passou a viver em uma cabana na floresta.  _x000D_
-_x000D_
-Um dia, uma mulher entrou correndo na cabana e caiu. Ela havia sido ferida por um lobo. O príncipe hesitou, mas cuidou da mulher mesmo assim. Ela, claro, ficou assustada com a aparência do homem e chorou.  </t>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>Era uma vez um príncipe que foi magicamente transformado numa fera feia. Desesperado com a própria aparência, abandonou seu país e viveu numa cabana na floresta.
+Um dia, uma mulher entrou correndo na cabana e caiu. Ela estava ferida por um lobo. O príncipe hesitou, mas cuidou da mulher mesmo assim. Ela, claro, se assustou com a visão do homem e chorou.</t>
         </is>
       </c>
     </row>
@@ -1096,11 +1092,10 @@
 They overcame many difficulties together and in the end, the curse on the prince was lifted. The two were married and lived happily ever after.</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Com o passar dos dias, ela começou a notar a bondade do homem. Ficou tocada por sua sinceridade e pela dor que ele carregava. Curada de seus ferimentos, decidiu viver com o homem.  _x000D_
-_x000D_
-Juntos, superaram muitas dificuldades e, no fim, a maldição do príncipe foi quebrada. Os dois se casaram e viveram felizes para sempre.  </t>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>Com a passagem dos dias, ela começou a notar a bondade do homem. Foi tocada pela sinceridade dele e pela dor que ele carregava. Curada dos ferimentos, decidiu viver com o homem.
+Venceram muitas dificuldades juntos e, no fim, a maldição sobre o príncipe foi desfeita. Os dois se casaram e viveram felizes para sempre.</t>
         </is>
       </c>
     </row>
@@ -1120,11 +1115,10 @@
 When I was a child, Master Cetrus told me this story over and over again. "Such a sad ending," he said. I wonder what he felt and what he wanted to tell me in this fairy tale humans wrote.</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uma história que está em todos os lugares.  _x000D_
-_x000D_
-Quando eu era criança, Mestre Cetrus me contou essa história repetidas vezes. "Que final triste", ele disse. Fico me perguntando o que ele sentiu e o que queria me dizer com esse conto de fadas escrito pelos humanos.  </t>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>Uma história que está em todo lugar.
+Quando era criança, o Lorde Cetrus me contava esta história repetidas vezes. “Que final triste,” dizia ele. Fico imaginando o que ele sentia e o que queria me dizer nesse conto de fadas que os humanos escreveram.</t>
         </is>
       </c>
     </row>
@@ -1154,9 +1148,9 @@
           <t>What is it?</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que é isso?  </t>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>Que é?</t>
         </is>
       </c>
     </row>
@@ -1184,9 +1178,9 @@
           <t>What is the old forest?</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que é a floresta antiga?  </t>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>O que é a floresta antiga?</t>
         </is>
       </c>
     </row>
@@ -1219,9 +1213,9 @@
           <t>Tell me about the power Eleas posses.</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fale-me sobre o poder que Eleas possui.  </t>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Conte-me o poder que os Elea possuem.</t>
         </is>
       </c>
     </row>
@@ -1254,9 +1248,9 @@
           <t>Tell me about the Dreaming Children.</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fale-me sobre as Crianças dos Sonhos.  </t>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>Conte-me as Crianças Sonhadoras.</t>
         </is>
       </c>
     </row>
@@ -1284,9 +1278,9 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Voltar)  </t>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>(Voltar)</t>
         </is>
       </c>
     </row>
@@ -1325,10 +1319,10 @@
 There still remain a few old forests on this continent as well. They don't take human lives like the forest of Vindale does, but they are dangerous places nonetheless.</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...No continente oriental, além do mar de Tyris, existe uma floresta profunda onde as pessoas nunca pisam. Uma floresta antiga onde os Eleas vivem. O veneno que as árvores exalam tira a racionalidade do homem e, eventualmente, o leva à morte. A floresta é chamada de Vindale... ou a Outra Floresta.  
-Ainda restam algumas florestas antigas neste continente também. Elas não tiram vidas humanas como a floresta de Vindale, mas ainda assim são lugares perigosos.  </t>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>...No continente oriental, do outro lado do mar de Tyris, há uma floresta funda onde ninguém põe o pé. Uma floresta antiga onde os Elea habitam. O veneno que as árvores exalam rouba a razão do homem e por fim o leva à morte. A floresta se chama Vindale... ou a Outra Floresta.
+Ainda restam algumas florestas antigas neste continente também. Elas não tiram vidas humanas como a floresta de Vindale, mas são lugares perigosos do mesmo jeito.</t>
         </is>
       </c>
     </row>
@@ -1363,9 +1357,9 @@
           <t>test</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>test</t>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>teste</t>
         </is>
       </c>
     </row>
@@ -1394,13 +1388,11 @@
 Fortunately or unfortunately, those powers are long lost to the Eleas who live in the world outside Vindale...well...except...except for the "Dreaming Children".</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você já ouviu falar do poder que os Eleas de Vindale possuem?  _x000D_
-_x000D_
-O miasma azul que preenche a floresta antiga também é chamado de "éter". Dizem que os antigos Eleas podiam manipular o éter para mover a terra e até mesmo invocar tempestades. Achei que essas coisas fossem apenas lendas... até testemunhar o milagre que o Mestre Cetrus realizou em Nymelle.  _x000D_
-_x000D_
-Felizmente ou infelizmente, esses poderes há muito se perderam para os Eleas que vivem no mundo fora de Vindale... bem... exceto... exceto pelas "Crianças dos Sonhos".  </t>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>Já ouviu falar do poder que os Elea de Vindale possuem?
+O miasma azul que enchia a floresta antiga também se chama "éter". Dizem que os Elea antigos podiam fiar o éter para mover a terra e até invocar tempestades. Eu achava que isso era só lenda... até testemunhar o milagre que o Lorde Cetrus invocou em Nymelle.
+Por sorte ou azar, esses poderes já se perderam há muito para os Elea que vivem no mundo fora de Vindale...bem...exceto...exceto pelas "Crianças Sonhadoras".</t>
         </is>
       </c>
     </row>
@@ -1433,16 +1425,14 @@
         <is>
           <t>Dreaming Children...poor children of Elea who can never grow up.
 Those who have developed the disease lose themselves between dreams and reality, and eventually fall into a sleep from which they will never awaken. Their faces are always vacant and their hearts are elusive as if detached from outside world.
-The ether dreams the Dreaming Children weave are embodied in reality as an outburst of power or an unforeseen calamity. I've heard a whole town vanished without a trace just because some idiot startled a Dreaming Child  in jest.</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crianças dos Sonhos... pobres crianças de Elea que nunca poderão crescer.  _x000D_
-_x000D_
-Aqueles que desenvolvem a doença perdem-se entre sonhos e realidade, e acabam caindo em um sono do qual jamais despertarão. Seus rostos estão sempre vazios e seus corações são inatingíveis, como se estivessem desconectados do mundo exterior.  _x000D_
-_x000D_
-Os sonhos de éter que as Crianças dos Sonhos tecem se manifestam na realidade como explosões de poder ou calamidades inesperadas. Ouvi dizer que uma cidade inteira desapareceu sem deixar rastros só porque um idiota assustou uma Criança dos Sonhos por brincadeira.  </t>
+The ether dreams the Dreaming Children weave are embodied in reality as an outburst of power or an unforeseen calamity. I've heard a whole town vanished without a trace just because some idiot startled a Dreaming Child in jest.</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>Crianças Sonhadoras... pobres crianças Elea que nunca podem crescer.
+As que desenvolvem a doença se perdem entre sonho e realidade, e acabam caindo num sono do qual jamais despertarão. Os rostos delas ficam sempre vazios e os corações, elusivos, como desligados do mundo.
+Os sonhos de éter que as Crianças Sonhadoras tecem se materializam na realidade como explosões de poder ou calamidades imprevistas. Ouvi dizer que uma cidade inteira sumiu sem rastro só porque algum idiota assustou uma Criança Sonhadora de brincadeira.</t>
         </is>
       </c>
     </row>
@@ -1462,11 +1452,10 @@
 ...Yes, it's a depressing story. But it's something you need to know if you're going to live here in Mysilia.</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ainda não foi encontrada cura para essa doença que chamamos de "o chamado da floresta". Perigosas em qualquer sociedade, elas são enviadas sozinhas para a floresta antiga, onde suas breves vidas chegam ao fim.  _x000D_
-_x000D_
-...Sim, é uma história deprimente. Mas é algo que você precisa saber se pretende viver aqui em Mysilia.  </t>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>Nenhuma cura foi ainda encontrada para a doença que chamamos de "chamado da floresta". Perigosas em qualquer sociedade, elas são mandadas sozinhas à floresta antiga e encerram suas vidas breves.
+...Sim, é uma história deprimente. Mas é algo que você precisa saber se vai viver aqui em Mysilia.</t>
         </is>
       </c>
     </row>
@@ -1484,9 +1473,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -1508,13 +1497,11 @@
 The dream... the voice of the girl...it...no, it can't be... I'm sorry, I'm being nonsense here.</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Quando criança, eu gostava de passar meu tempo na floresta antiga. O Mestre Cetrus costumava rir de mim quando eu dizia que talvez fosse um Elea.  _x000D_
-_x000D_
-Quando durmo à sombra das grandes árvores da floresta antiga, às vezes tenho sonhos estranhos. Sonhos com um rio preenchido por um brilho azul... sua correnteza parece perigosa, mas sou irresistivelmente atraído por ela. E sempre que tento me aproximar do rio, ouço a voz de uma garota dizendo: "Não vá para lá. Não siga esse caminho".  _x000D_
-_x000D_
-O sonho... a voz da garota... isso... não, não pode ser... Desculpe, estou falando bobagens.  </t>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>...Eu gostava de passar meu tempo na floresta antiga quando era criança. O Lorde Cetrus vivia rindo de mim quando eu dizia que talvez eu fosse Elea.
+Quando durmo à sombra das árvores grandes da floresta antiga, às vezes tenho sonhos estranhos. Sonhos com um rio cheio de um fulgor azul... a corrente dele parece perigosa, mas sou irresistivelmente atraída a ele. E sempre que tento me aproximar do rio, ouço a voz de uma garota dizendo: "Não vá para lá. Não siga por esse caminho".
+O sonho... a voz da garota...isso...não, não pode ser... Desculpa, estou falando bobagem.</t>
         </is>
       </c>
     </row>
@@ -1538,28 +1525,37 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>私の夢を見た？</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>I wish you would die.</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Eu desejo que você morra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="74.59999999999999" customHeight="1" s="9">
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="12.8" customHeight="1" s="9">
       <c r="H92" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="I92" s="12" t="inlineStr">
-        <is>
-          <t>…そう、よほどひどく頭を打ったのね。まずはしっかり休養をとるためにもベッドを作ってみたらどう？
-眠い時に「瞑想」を行うことでも睡眠はとれるけど、ベッドを使えばいつでも休むことができるし、疲労回復の効果も高いのよ。</t>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -1591,9 +1587,9 @@
           <t>I wish you would die.</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Eu gostaria que você morresse.</t>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>Tomara que você morra.</t>
         </is>
       </c>
     </row>
@@ -1640,11 +1636,10 @@
 Before we arrived here, a cute little puppy grew attached to me... It followed us everywhere. The puppy, curious as it was, ran off after something while we were resting and didn't come back.</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não é que eu não goste de humanos, mas sempre senti uma conexão mais profunda com os animais. Sempre acabo domesticando os animais que encontro enquanto viajo.  _x000D_
-_x000D_
-Antes de chegarmos aqui, um filhote adorável se apegou a mim... Ele nos seguia para todo lado. Mas, curioso como era, correu atrás de alguma coisa enquanto descansávamos e não voltou.  </t>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>Não é que eu não goste de humanos, mas sempre senti uma ligação mais funda com os animais. Acabo domando os bichos que encontro quando viajo.
+Antes de chegarmos aqui, um cachorrinho fofo se apegou a mim... Seguia a gente para todo lado. O cachorrinho, curioso como era, saiu correndo atrás de algo enquanto descansávamos e não voltou.</t>
         </is>
       </c>
     </row>
@@ -1664,11 +1659,10 @@
 It's not a very dangerous place, so can you go and look for the little one? The cave is just northwest of here.</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Havia uma caverna perto de onde estávamos descansando naquela hora. Estou preocupado que o filhote possa ter se perdido dentro dela.  _x000D_
-_x000D_
-Não é um lugar muito perigoso, então você poderia ir procurar pelo pequeno? A caverna fica logo a noroeste daqui.  </t>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>Havia uma caverna perto de onde descansávamos naquela época. Fico preocupada de o cachorrinho ter se metido no fundo dela.
+Não é um lugar muito perigoso, então pode ir procurar o pequeno? A caverna fica a noroeste daqui.</t>
         </is>
       </c>
     </row>
@@ -1716,11 +1710,11 @@
 Poppy, don't go off on your own, okay? Let this adventurer take good care of you from now on.</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Ah, então ele realmente entrou na caverna. Que alívio saber que está seguro.  
-Agradeço por ter encontrado o pequeno. Aqui, preparei uma recompensa para você.  
-Poppy, não vá sozinho por aí, ok? Deixe que este aventureiro cuide bem de você a partir de agora."  </t>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>Ah, então ele se meteu na caverna mesmo. Que alívio saber que está bem.
+Agradeço por achar o pequeno. Aqui, preparei uma recompensa para você.
+Poppy, não saia por aí sozinho, tá? Deixe este aventureiro cuidar bem de você de agora em diante.</t>
         </is>
       </c>
     </row>
@@ -1772,9 +1766,9 @@
           <t xml:space="preserve">It seems you're getting accustomed to life around here. I'll give you a few craft recipes that might be useful in your future endeavors. </t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parece que você está se acostumando com a vida por aqui. Vou te passar algumas receitas de artesanato que podem ser úteis em suas futuras jornadas.  </t>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parece que você está se acostumando à vida por aqui. Vou te dar algumas receitas de fabricação que podem ser úteis nos seus próximos passos. </t>
         </is>
       </c>
     </row>
@@ -1794,11 +1788,10 @@
 ...Nymelle, also known as the Graveyard of Winds, has been the site of numerous strange occurrences for years. I can feel it too - something is happening deep within that cave.</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ash mencionou que lhe designou para explorar a caverna.  _x000D_
-_x000D_
-...Nymelle, também conhecida como o Cemitério dos Ventos, tem sido palco de inúmeros acontecimentos estranhos há anos. Eu também posso sentir – algo está acontecendo no fundo daquela caverna.  </t>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>O Ash comentou de te designar para explorar a caverna.
+...Nymelle, também conhecida como Cemitério dos Ventos, é palco de inúmeros acontecimentos estranhos há anos. Sinto também: algo acontece no fundo daquela caverna.</t>
         </is>
       </c>
     </row>
@@ -1818,11 +1811,10 @@
 May the wind always follow you, #pc.</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não sabemos que perigos podem estar à espreita, então tenha extremo cuidado.  _x000D_
-_x000D_
-Que o vento sempre o acompanhe, #pc.  </t>
+      <c r="K119" s="8" t="inlineStr">
+        <is>
+          <t>Não sabemos que perigos podem nos aguardar, então muito cuidado.
+Que o vento sempre te siga, #pc.</t>
         </is>
       </c>
     </row>
@@ -1867,10 +1859,10 @@
 You'll eventually find some locked chests in dungeons, and you'll need a 'lockpick' to open them. I’ve placed a chest at your feet. Try opening it with this lockpick.</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Antes de você ir para Nymelle, há algo que quero lhe ensinar.  
-Em algum momento, você encontrará baús trancados em masmorras, e precisará de uma 'gazua' para abri-los. Coloquei um baú aos seus pés. Tente abri-lo com esta gazua.</t>
+      <c r="K126" s="8" t="inlineStr">
+        <is>
+          <t>Antes de ir a Nymelle, há algo que quero te ensinar.
+Você vai encontrar baús trancados nas masmorras, e precisará de uma 'chave-mestra' para abri-los. Coloquei um baú aos seus pés. Tente abri-lo com esta chave-mestra.</t>
         </is>
       </c>
     </row>
@@ -1922,13 +1914,11 @@
 Even if you have a lockpick, you can't open it if your skill is too low. Remember that.</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não conseguiu abrir?  _x000D_
-_x000D_
-...Sim, isso porque eu tranquei esse baú com cuidado.  _x000D_
-_x000D_
-Mesmo que você tenha uma gazua, não conseguirá abri-lo se sua habilidade for muito baixa. Lembre-se disso.  </t>
+      <c r="K132" s="8" t="inlineStr">
+        <is>
+          <t>Não abre?
+...Sim, é porque eu tranquei aquele baú com cuidado.
+Mesmo com uma chave-mestra, não abre se sua perícia estiver baixa demais. Lembre disso.</t>
         </is>
       </c>
     </row>
@@ -1946,9 +1936,9 @@
           <t>You can have the lockpick and the chest. When you become a seasoned adventurer, you will surely find the contents within useful.</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode ficar com a gazua e o baú. Quando se tornar um aventureiro experiente, certamente achará o conteúdo útil.  </t>
+      <c r="K133" s="8" t="inlineStr">
+        <is>
+          <t>Pode ficar com a chave-mestra e o baú. Quando virar um aventureiro experiente, certamente achará o conteúdo útil.</t>
         </is>
       </c>
     </row>
@@ -2001,11 +1991,10 @@
 Ash seems to be enjoying too... I must be grateful to you for that. </t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O tempo voa, não é? Já faz uma semana desde que nos conhecemos neste campo._x000D_
-_x000D_
-Ash parece estar se divertindo também... devo agradecer a você por isso.  </t>
+      <c r="K145" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O tempo voa, né? Já faz uma semana desde que nos encontramos nesta campina.
+O Ash parece estar gostando também... Devo essa gratidão a você. </t>
         </is>
       </c>
     </row>
@@ -2025,11 +2014,10 @@
 I’ve been wanting to ask you—what do you want to do from now on?</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No começo, você parecia um pouco incerto, mas agora parece que já pegou o jeito de viver aqui. Talvez esteja começando a enxergar seus objetivos com mais clareza.  _x000D_
-_x000D_
-Tenho vontade de te perguntar—o que você quer fazer a partir de agora?  </t>
+      <c r="K146" s="8" t="inlineStr">
+        <is>
+          <t>No começo, você parecia um pouco perdido, mas agora parece que pegou o jeito de viver aqui. Talvez esteja começando a ver seus objetivos com mais clareza.
+Queria te perguntar: o que você quer fazer daqui para frente?</t>
         </is>
       </c>
     </row>
@@ -2057,9 +2045,9 @@
           <t>I want to explore Nefia.</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero explorar Nefia.  </t>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Quero explorar Nefia.</t>
         </is>
       </c>
     </row>
@@ -2087,9 +2075,9 @@
           <t>I want to focus on developing my land.</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero focar no desenvolvimento da minha terra.  </t>
+      <c r="K148" s="8" t="inlineStr">
+        <is>
+          <t>Quero me concentrar em desenvolver minha terra.</t>
         </is>
       </c>
     </row>
@@ -2117,9 +2105,9 @@
           <t>I want to visit various places.</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero visitar vários lugares.  </t>
+      <c r="K149" s="8" t="inlineStr">
+        <is>
+          <t>Quero visitar vários lugares.</t>
         </is>
       </c>
     </row>
@@ -2148,9 +2136,9 @@
           <t>I want to do jobs you can’t tell anyone about.</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero fazer trabalhos que ninguém pode saber.  </t>
+      <c r="K150" s="8" t="inlineStr">
+        <is>
+          <t>Quero fazer trabalhos que não se possa contar a ninguém.</t>
         </is>
       </c>
     </row>
@@ -2178,9 +2166,9 @@
           <t>I want to do nothing.</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero não fazer nada.  </t>
+      <c r="K151" s="8" t="inlineStr">
+        <is>
+          <t>Quero não fazer nada.</t>
         </is>
       </c>
     </row>
@@ -2208,9 +2196,9 @@
           <t>I want to die.</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quero morrer.  </t>
+      <c r="K152" s="8" t="inlineStr">
+        <is>
+          <t>Quero morrer.</t>
         </is>
       </c>
     </row>
@@ -2245,10 +2233,10 @@
 Hehe, speaking of which, I have something that’s just perfect for you. It's alright, do not hesitate.</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo... #last_choice...? Essa é bem a sua cara.  
-Hehe, falando nisso, tenho algo que combina perfeitamente com você. Está tudo bem, não hesite.  </t>
+      <c r="K156" s="8" t="inlineStr">
+        <is>
+          <t>Entendo... #last_choice...? Uma resolução bem do seu jeito.
+Hehe, falando nisso, tenho algo perfeito para você. Pode confiar, não hesite.</t>
         </is>
       </c>
     </row>
